--- a/experimental_datasets/Schiebinger/Data/CardamomOT_inputs.xlsx
+++ b/experimental_datasets/Schiebinger/Data/CardamomOT_inputs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17200" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="readme" sheetId="1" state="visible" r:id="rId1"/>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,11 +55,17 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +80,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -106,11 +117,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -287,10 +301,15 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>Optional: dataset_id whose schedule these rows replace (empty or "all": default schedule of every sample)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
         <t>Timepoint (optional: without times, rows follow the sorted timepoints of the data)</t>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>Value of stimulus 1 at this timepoint (default: 0 at the first timepoint, 1 after)</t>
       </text>
@@ -754,43 +773,43 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" style="8" min="1" max="1"/>
-    <col width="95" customWidth="1" style="8" min="2" max="2"/>
-    <col width="45" customWidth="1" style="8" min="3" max="3"/>
+    <col width="28" customWidth="1" style="9" min="1" max="1"/>
+    <col width="95" customWidth="1" style="9" min="2" max="2"/>
+    <col width="45" customWidth="1" style="9" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19" customHeight="1" s="8">
+    <row r="1" ht="19" customHeight="1" s="9">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CardamomOT — optional inputs of the run</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1" s="8">
-      <c r="A2" s="7" t="inlineStr">
+    <row r="2" ht="45" customHeight="1" s="9">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Fill only what you need: empty cells mean "not given" and the defaults of CardamomOT apply. Each sheet holds one kind of information; the header cells carry a comment (hover them) explaining their content.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1" s="8">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="3" ht="45" customHeight="1" s="9">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Text files of older projects (genes_queries.txt, KO_OV_simulate.txt, stimulus_schedule.txt...) still present in Data/ are imported into this workbook at each run and OVERWRITE the corresponding cells (a warning is printed): delete them to edit the workbook instead.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1" s="8">
-      <c r="A4" s="7" t="inlineStr">
+    <row r="4" ht="45" customHeight="1" s="9">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Large numeric arrays stay files in Data/: reference_network.csv (structural prior), basal_init / basal_ref, inter_init / inter_ref (.npy or .csv), inter_simul_ref (.npy or .csv).</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1" s="8">
-      <c r="A5" s="7" t="n"/>
+    <row r="5" ht="45" customHeight="1" s="9">
+      <c r="A5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -809,180 +828,180 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1" s="8">
+    <row r="7" ht="48" customHeight="1" s="9">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>model_parameters</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Parameters of the model for this project, grouped by use: empty value = default of CardamomOT/model/base.py; a filled value overrides it, and the command-line options override the workbook.</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n"/>
-    </row>
-    <row r="8" ht="48" customHeight="1" s="8">
+      <c r="C7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="48" customHeight="1" s="9">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>gene_lists</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Gene lists, one gene per row in each column. Any other column is a named gene list, usable as the targets (STIMk) or a RATE target of perturbation_inference and perturbation_simulation (exported as gene_list_&lt;name&gt;.txt; legacy Data/gene_list_&lt;name&gt;.txt).</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>genes_queries.txt, proliferation_signatures.txt/.csv, death_signatures.txt/.csv, senescence_signatures.txt/.csv</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1" s="8">
+    <row r="9" ht="48" customHeight="1" s="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>stimulus_inference_schedule</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Schedule of the stimuli of the measured data (inference); one row per timepoint, one column per stimulus (add stimulus_2, stimulus_3... for several stimuli; without this sheet: one stimulus). Rows with a sample_id give the schedule of that sample only (e.g. an untreated control at 0).</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>stimulus_schedule_inference.txt, stimulus_schedule.txt</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1" s="8">
+    <row r="10" ht="48" customHeight="1" s="9">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>stimulus_test_schedule</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Schedule of the inference stimuli for the held-out cells (infer_test): test split and samples removed from the inference (perturbation_inference, remove_from_inference). Empty: the inference schedule.</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n"/>
-    </row>
-    <row r="11" ht="48" customHeight="1" s="8">
+      <c r="C10" s="8" t="n"/>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="9">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>stimulus_simulation_schedule</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Schedules of the simulations, one row per simulated timepoint: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation).</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>stimulus_schedule_simulate.txt, stimulus_schedule_simul.txt</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1" s="8">
+    <row r="12" ht="48" customHeight="1" s="9">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>perturbation_inference</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Perturbations of the measured data, used by the inference: genetic perturbations of samples (KO / OV), samples held out for validation (remove_from_inference, reference_sample), and the inference stimuli (row sample_id = all: targets STIMk and effects on proliferation RATEk, k = column of stimulus_inference_schedule). Empty: one stimulus, every gene a possible target, no effect on the rates.</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>KO_OV_inference.txt, stimulus_targets.txt/.csv</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1" s="8">
+    <row r="13" ht="48" customHeight="1" s="9">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>perturbation_simulation</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>In-silico perturbations simulated by simulate_network_KOV, one condition per row (add STIM2, STIM3... for several perturbation stimuli; their effects add up).</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>KO_OV_Stim_simulate.txt, KO_OV_simulate.txt</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1" s="8">
+    <row r="14" ht="48" customHeight="1" s="9">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>times</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Timepoints, one per row.</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>times_to_inference.txt, times_to_simulate.txt</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="48" customHeight="1" s="8">
+    <row r="15" ht="48" customHeight="1" s="9">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>proliferation_rates</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Anchors of the net proliferation rates per cell type (get_proliferation_rates); every cell type needs a value.</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>proliferation_rates.txt/.csv</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="48" customHeight="1" s="8">
+    <row r="16" ht="48" customHeight="1" s="9">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>population_sizes</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>Absolute population sizes, anchoring the growth estimated by optimal transport.</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>population_sizes.txt/.csv</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1" s="8">
+    <row r="17" ht="48" customHeight="1" s="9">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>transition_rates</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>Cell-type transition rate matrix constraining optimal transport: first column = source cell types, header = target cell types (as in obs cell_type_transition, else cell_type).</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>transition_rates.txt/.csv</t>
         </is>
@@ -1006,10 +1025,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="8" min="1" max="1"/>
-    <col width="21" customWidth="1" style="8" min="2" max="2"/>
+    <col width="16" customWidth="1" style="9" min="1" max="1"/>
+    <col width="21" customWidth="1" style="9" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1037,10 +1056,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="8" min="1" max="1"/>
-    <col width="19" customWidth="1" style="8" min="2" max="2"/>
+    <col width="16" customWidth="1" style="9" min="1" max="1"/>
+    <col width="19" customWidth="1" style="9" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1068,9 +1087,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="8" min="1" max="1"/>
+    <col width="16" customWidth="1" style="9" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1093,11 +1112,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" style="8" min="1" max="1"/>
-    <col width="14" customWidth="1" style="8" min="2" max="2"/>
-    <col width="120" customWidth="1" style="8" min="3" max="3"/>
+    <col width="30" customWidth="1" style="9" min="1" max="1"/>
+    <col width="14" customWidth="1" style="9" min="2" max="2"/>
+    <col width="120" customWidth="1" style="9" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,91 +1145,91 @@
       <c r="B2" s="6" t="n"/>
       <c r="C2" s="6" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="8">
+    <row r="3" ht="16" customHeight="1" s="9">
       <c r="A3" t="inlineStr">
         <is>
           <t>estimate_proliferation_rates</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>get_proliferation_rates: obs['proliferation_net_rate'] from gene signatures, anchored to Data/proliferation_rates</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="8">
+    <row r="4" ht="16" customHeight="1" s="9">
       <c r="A4" t="inlineStr">
         <is>
           <t>simulate_with_proliferation</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>apply branching process in simulate_trajectories_unitary</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="8">
+    <row r="5" ht="16" customHeight="1" s="9">
       <c r="A5" t="inlineStr">
         <is>
           <t>select_genes</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>select_genes_and_split: gene selection (queries, entropy genes, global network, Steiner tree); False = all genes kept</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="8">
+    <row r="6" ht="16" customHeight="1" s="9">
       <c r="A6" t="inlineStr">
         <is>
           <t>build_prior_network</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>literature prior cardamomOT/ref_network.csv: built by the gene selection if select_genes, else by build_reference_network</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" s="8">
+    <row r="7" ht="16" customHeight="1" s="9">
       <c r="A7" t="inlineStr">
         <is>
           <t>simulate_perturbations</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>simulate_network_KOV + check_KOV_to_sim (Data/KO_OV_Stim_simulate)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" s="8">
+    <row r="8" ht="16" customHeight="1" s="9">
       <c r="A8" t="inlineStr">
         <is>
           <t>run_test</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>infer_test + check_test_to_train on the held-out cells (needs split = 'train')</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" s="8">
+    <row r="9" ht="16" customHeight="1" s="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>split</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>'train': train/test split of the cells (train_rate per sample and time); 'full': all cells</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" s="8">
+    <row r="10" ht="16" customHeight="1" s="9">
       <c r="A10" t="inlineStr">
         <is>
           <t>train_rate</t>
@@ -1219,19 +1238,19 @@
       <c r="B10" t="n">
         <v>0.1</v>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>share of the cells of each (sample, time) in the train split (at least 100); the test keeps at most as many</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" s="8">
+    <row r="11" ht="16" customHeight="1" s="9">
       <c r="A11" t="inlineStr">
         <is>
           <t>species</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>'auto' (from gene names), 'human' or 'mouse': degradation rates, proliferation signatures, literature prior</t>
         </is>
@@ -1246,97 +1265,97 @@
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
     </row>
-    <row r="13" ht="16" customHeight="1" s="8">
+    <row r="13" ht="16" customHeight="1" s="9">
       <c r="A13" t="inlineStr">
         <is>
           <t>num_max_genes</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>budget: number of selected genes (stimuli excluded)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1" s="8">
+    <row r="14" ht="16" customHeight="1" s="9">
       <c r="A14" t="inlineStr">
         <is>
           <t>n_query_genes</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>at most this many genes of Data/genes_queries.txt (round robin over time/cell-type DE groups)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1" s="8">
+    <row r="15" ht="16" customHeight="1" s="9">
       <c r="A15" t="inlineStr">
         <is>
           <t>n_entropy_genes</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>at least this many entropy genes (Gandrillon KD &amp; MDE), same round robin; n_query + n_entropy &lt; num_max_genes</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" s="8">
+    <row r="16" ht="16" customHeight="1" s="9">
       <c r="A16" t="inlineStr">
         <is>
           <t>network_method</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>global network: 'otvelo_granger', 'otvelo_corr', or &lt;project&gt;/network_methods/&lt;name&gt;.py</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1" s="8">
+    <row r="17" ht="16" customHeight="1" s="9">
       <c r="A17" t="inlineStr">
         <is>
           <t>k_in_steiner</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>strongest incoming edges kept per gene in the Steiner graph</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1" s="8">
+    <row r="18" ht="16" customHeight="1" s="9">
       <c r="A18" t="inlineStr">
         <is>
           <t>closure_min</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>closure: add the gene bringing the most probable regulation (sum of w) to the selection while &gt;= this</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1" s="8">
+    <row r="19" ht="16" customHeight="1" s="9">
       <c r="A19" t="inlineStr">
         <is>
           <t>min_entropy_change</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>variability floor of the selection: max BUB-entropy change between consecutive times (bits, Gandrillon MDE)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1" s="8">
+    <row r="20" ht="16" customHeight="1" s="9">
       <c r="A20" t="inlineStr">
         <is>
           <t>min_nb_separation</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>... and separation of the extreme NB modes at the mixture initialization (times / cell types, batch_size_mixture cells per time)</t>
         </is>
@@ -1351,61 +1370,61 @@
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
     </row>
-    <row r="22" ht="16" customHeight="1" s="8">
+    <row r="22" ht="16" customHeight="1" s="9">
       <c r="A22" t="inlineStr">
         <is>
           <t>prior_network_pen</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>1 if we don't use prior information. If not we can penalize the non-existing age in prior network with values between 1 and 0: 0 = impossible edge</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1" s="8">
+    <row r="23" ht="16" customHeight="1" s="9">
       <c r="A23" t="inlineStr">
         <is>
           <t>max_free_params</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>change=1 with ref=1 and prior 0 (hard prior): gene budget set so that the literature prior leaves this many free network parameters</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1" s="8">
+    <row r="24" ht="16" customHeight="1" s="9">
       <c r="A24" t="inlineStr">
         <is>
           <t>literature_selection</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>reweight edge probabilities by OmniPath feasibility and write the literature prior (ref_network.csv)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1" s="8">
+    <row r="25" ht="16" customHeight="1" s="9">
       <c r="A25" t="inlineStr">
         <is>
           <t>literature_depth</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>max path length in the literature graph (last edge TF -&gt; target)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1" s="8">
+    <row r="26" ht="16" customHeight="1" s="9">
       <c r="A26" t="inlineStr">
         <is>
           <t>literature_resources</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>'extended' (OmniPath, CollecTRI + PathwayExtra, KinaseExtra, LigRecExtra, DoRothEA A-D, TFtarget) or 'core' (OmniPath + CollecTRI)</t>
         </is>
@@ -1420,13 +1439,13 @@
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
     </row>
-    <row r="28" ht="16" customHeight="1" s="8">
+    <row r="28" ht="16" customHeight="1" s="9">
       <c r="A28" t="inlineStr">
         <is>
           <t>stimulus</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>1 if we simulate with a stimulus. If not we can penalize the stimulus with a value between 1 and 0: 0 = no sitmulus</t>
         </is>
@@ -1441,61 +1460,61 @@
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="6" t="n"/>
     </row>
-    <row r="30" ht="16" customHeight="1" s="8">
+    <row r="30" ht="16" customHeight="1" s="9">
       <c r="A30" t="inlineStr">
         <is>
           <t>use_depth_factor</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>use obs['depth_factor'] (estimate_cell_depth) in the NB model and simulations; False = s_i = 1 (an existing factor is kept but ignored)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1" s="8">
+    <row r="31" ht="16" customHeight="1" s="9">
       <c r="A31" t="inlineStr">
         <is>
           <t>compute_depth_factor</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>estimate_cell_depth computes the diagnostic and writes obs['depth_factor'] if needed; False = only reads an existing factor (never removed)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1" s="8">
+    <row r="32" ht="16" customHeight="1" s="9">
       <c r="A32" t="inlineStr">
         <is>
           <t>allow_depth_correction</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>estimate_cell_depth: apply the per-cell depth factor s_i when the diagnostic recommends it</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1" s="8">
+    <row r="33" ht="16" customHeight="1" s="9">
       <c r="A33" t="inlineStr">
         <is>
           <t>depth_method</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>depth factor: 'group_median', 'poissonian' (Fang &amp; Pachter, 2025), or &lt;project&gt;/depth_methods/&lt;name&gt;.py</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1" s="8">
+    <row r="34" ht="16" customHeight="1" s="9">
       <c r="A34" t="inlineStr">
         <is>
           <t>depth_by_cell_type</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>estimate s_i within (sample, time, cell type) groups; False = (sample, time) only:</t>
         </is>
@@ -1510,61 +1529,61 @@
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="6" t="n"/>
     </row>
-    <row r="36" ht="16" customHeight="1" s="8">
+    <row r="36" ht="16" customHeight="1" s="9">
       <c r="A36" t="inlineStr">
         <is>
           <t>mean_forcing_em</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>at which point we force the mean correction: the higher the more</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1" s="8">
+    <row r="37" ht="16" customHeight="1" s="9">
       <c r="A37" t="inlineStr">
         <is>
           <t>batch_size_mixture</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Maximum number of cells per time used for mixture calibration in the inference.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1" s="8">
+    <row r="38" ht="16" customHeight="1" s="9">
       <c r="A38" t="inlineStr">
         <is>
           <t>soft_em_refinement</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>NB mixture: refine (ks, c) by soft EM with fixed basin masses</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="16" customHeight="1" s="8">
+    <row r="39" ht="16" customHeight="1" s="9">
       <c r="A39" t="inlineStr">
         <is>
           <t>integrate_samples</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>in [0, 1]: per-sample mixtures pushed towards the common target (1 = equal parameters, 0 = own fits)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="16" customHeight="1" s="8">
+    <row r="40" ht="16" customHeight="1" s="9">
       <c r="A40" t="inlineStr">
         <is>
           <t>ref_sample_integration</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>dataset_id of the reference sample; None = cell-weighted average of mode means (keeps total counts)</t>
         </is>
@@ -1579,73 +1598,73 @@
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="6" t="n"/>
     </row>
-    <row r="42" ht="16" customHeight="1" s="8">
+    <row r="42" ht="16" customHeight="1" s="9">
       <c r="A42" t="inlineStr">
         <is>
           <t>force_basins</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Do we want to ensure the means to be preserved by the NB mixture ? It may not preserve multistability</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1" s="8">
+    <row r="43" ht="16" customHeight="1" s="9">
       <c r="A43" t="inlineStr">
         <is>
           <t>temporal_basins</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>Is it preserved temporally ?</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1" s="8">
+    <row r="44" ht="16" customHeight="1" s="9">
       <c r="A44" t="inlineStr">
         <is>
           <t>min_n_loops</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>minimal number of iterations in inference loops</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="16" customHeight="1" s="8">
+    <row r="45" ht="16" customHeight="1" s="9">
       <c r="A45" t="inlineStr">
         <is>
           <t>max_iter</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>max iteration for main loop</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="16" customHeight="1" s="8">
+    <row r="46" ht="16" customHeight="1" s="9">
       <c r="A46" t="inlineStr">
         <is>
           <t>batch_size_traj</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Maximum number of cells used per time point per sample for solving EOT problems in the inference.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="16" customHeight="1" s="8">
+    <row r="47" ht="16" customHeight="1" s="9">
       <c r="A47" t="inlineStr">
         <is>
           <t>n_network_fits</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>Theta = mean of min(n_network_fits, 1 + n_states // batch_size) fits on disjoint subsamples, at every network update</t>
         </is>
@@ -1660,37 +1679,37 @@
       <c r="B48" s="6" t="n"/>
       <c r="C48" s="6" t="n"/>
     </row>
-    <row r="49" ht="16" customHeight="1" s="8">
+    <row r="49" ht="16" customHeight="1" s="9">
       <c r="A49" t="inlineStr">
         <is>
           <t>growth_reg_source</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>source-marginal relaxation (x log G) of the growth OT pass: small = data-driven but noisy, large = prior kept</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1" s="8">
+    <row r="50" ht="16" customHeight="1" s="9">
       <c r="A50" t="inlineStr">
         <is>
           <t>prolif_uses_stimulus</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>inference stimuli are inputs of the ProliferationMLP, R(u, P) (no effect if constant over the intervals)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="16" customHeight="1" s="8">
+    <row r="51" ht="16" customHeight="1" s="9">
       <c r="A51" t="inlineStr">
         <is>
           <t>simulation_stochastic</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>1 if we simulate Bursty-like proteins, 0 if deterministic limit for proteins</t>
         </is>
@@ -1705,13 +1724,13 @@
       <c r="B52" s="6" t="n"/>
       <c r="C52" s="6" t="n"/>
     </row>
-    <row r="53" ht="16" customHeight="1" s="8">
+    <row r="53" ht="16" customHeight="1" s="9">
       <c r="A53" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>Random seed for reproducibility (main process and parallel workers); None = not seeded (runs vary)</t>
         </is>
@@ -1729,13 +1748,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:D86"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" style="8" min="1" max="1"/>
-    <col width="28" customWidth="1" style="8" min="2" max="2"/>
-    <col width="20" customWidth="1" style="8" min="3" max="3"/>
-    <col width="25" customWidth="1" style="8" min="4" max="4"/>
+    <col width="17" customWidth="1" style="9" min="1" max="1"/>
+    <col width="28" customWidth="1" style="9" min="2" max="2"/>
+    <col width="20" customWidth="1" style="9" min="3" max="3"/>
+    <col width="25" customWidth="1" style="9" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1757,6 +1776,601 @@
       <c r="D1" s="4" t="inlineStr">
         <is>
           <t>senescence_signatures</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Pou5f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Klf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sox2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Myc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Egfp</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Fut9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Shisa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dmrtc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Zic3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pou3f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Id3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Nfix</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Nfic</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Prrx1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Nanog</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Zfp42</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Zpf42</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dppa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Esrrb</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Mybl2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Elf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tgif1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Klf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Etv5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Cdc5l</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Spic</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Hesx1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Msc</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Obox6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sohlh2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ddit3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bhlhe40</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Xist</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Ooep</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Fmr1nb</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Lncenc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Tcl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Gata3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Elf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Mycn</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ovol2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Ascl2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Phlda2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cited2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Rhox6</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Rhox9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Batf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Pparg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Myt1l</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Hnf1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Prdm11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gata2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gcm1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Msx2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Hoxd13</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Nr1h4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Hand1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Bbx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Wnt7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Prr5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Pdgfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Cyb5r3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Cenpm</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Srebf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Pmm1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cdkn2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cdkn2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cdkn2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Cdk13</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Mapk9</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Rarb</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Foxp2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Emx1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Pou3f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Nr2f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Neurod4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Scrt2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Nhlh2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Pou2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Onecut1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Tal2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Barhl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Pitx2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Msx1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Msx3</t>
         </is>
       </c>
     </row>
@@ -1772,173 +2386,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="8" min="1" max="4"/>
-    <col width="16" customWidth="1" style="8" min="2" max="2"/>
-    <col width="16" customWidth="1" style="8" min="3" max="3"/>
-    <col width="16" customWidth="1" style="8" min="4" max="4"/>
+    <col width="16" customWidth="1" style="9" min="1" max="4"/>
+    <col width="16" customWidth="1" style="9" min="2" max="2"/>
+    <col width="16" customWidth="1" style="9" min="3" max="3"/>
+    <col width="16" customWidth="1" style="9" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>stimulus_1</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>stimulus_2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
+      <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1955,9 +2574,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="8" min="1" max="3"/>
+    <col width="16" customWidth="1" style="9" min="1" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1990,9 +2609,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="8" min="1" max="4"/>
+    <col width="16" customWidth="1" style="9" min="1" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2030,12 +2649,12 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="8" min="1" max="3"/>
-    <col width="25" customWidth="1" style="8" min="4" max="4"/>
-    <col width="20" customWidth="1" style="8" min="5" max="5"/>
-    <col width="16" customWidth="1" style="8" min="6" max="8"/>
+    <col width="16" customWidth="1" style="9" min="1" max="3"/>
+    <col width="25" customWidth="1" style="9" min="4" max="4"/>
+    <col width="20" customWidth="1" style="9" min="5" max="5"/>
+    <col width="16" customWidth="1" style="9" min="6" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2093,19 +2712,18 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="8" min="1" max="5"/>
-    <col width="16" customWidth="1" style="8" min="2" max="2"/>
+    <col width="16" customWidth="1" style="9" min="1" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>KO</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>OV</t>
         </is>
@@ -2138,10 +2756,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="8" min="1" max="1"/>
-    <col width="21" customWidth="1" style="8" min="2" max="2"/>
+    <col width="22" customWidth="1" style="9" min="1" max="1"/>
+    <col width="21" customWidth="1" style="9" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/experimental_datasets/Schiebinger/Data/CardamomOT_inputs.xlsx
+++ b/experimental_datasets/Schiebinger/Data/CardamomOT_inputs.xlsx
@@ -244,6 +244,11 @@
         <t>Total population size at this timepoint</t>
       </text>
     </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional: dataset_id of the sample (empty or "all": default of the samples without rows)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -477,6 +482,11 @@
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>Reference net proliferation rate (birth - death), in h^-1; without the inference stimulus if perturbation_inference gives its effect on this cell type (RATEk)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional: dataset_id these anchors are for (empty or "all": default of the samples that have none of their own)</t>
       </text>
     </comment>
   </commentList>
@@ -1024,11 +1034,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="9" min="1" max="1"/>
     <col width="21" customWidth="1" style="9" min="2" max="2"/>
+    <col width="16" customWidth="1" style="9" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1040,6 +1051,11 @@
       <c r="B1" s="4" t="inlineStr">
         <is>
           <t>net_rate_per_hour</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>sample_id</t>
         </is>
       </c>
     </row>
@@ -1055,11 +1071,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="9" min="1" max="1"/>
     <col width="19" customWidth="1" style="9" min="2" max="2"/>
+    <col width="16" customWidth="1" style="9" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1071,6 +1088,11 @@
       <c r="B1" s="4" t="inlineStr">
         <is>
           <t>population_size</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>sample_id</t>
         </is>
       </c>
     </row>

--- a/experimental_datasets/Schiebinger/Data/CardamomOT_inputs.xlsx
+++ b/experimental_datasets/Schiebinger/Data/CardamomOT_inputs.xlsx
@@ -487,6 +487,16 @@
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>Optional: dataset_id these anchors are for (empty or "all": default of the samples that have none of their own)</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional reference birth (division) rate, in h^-1: anchors the birth rate of the cells of this type (dilution of the proteins); with the net rate, gives the death rate</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional reference death rate, in h^-1: anchors the death rate of the cells of this type; with the net rate, gives the birth rate</t>
       </text>
     </comment>
   </commentList>
@@ -859,7 +869,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Gene lists, one gene per row in each column. Any other column is a named gene list, usable as the targets (STIMk) or a RATE target of perturbation_inference and perturbation_simulation (exported as gene_list_&lt;name&gt;.txt; legacy Data/gene_list_&lt;name&gt;.txt).</t>
+          <t>Gene lists, one gene per row in each column. Any other column is a named gene list, usable as the targets (STIMk) or a RATE target of perturbation_inference and perturbation_simulation (exported as gene_list_&lt;name&gt;.txt).</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -906,7 +916,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Schedules of the simulations, one row per simulated timepoint: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation).</t>
+          <t>Schedules of the simulations: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation). Rows with a scenario name give alternative schedules (e.g. alternating inference and perturbation stimuli), simulated for the conditions that ask for them; a value applies to the simulated intervals ending at or after its time, so switching times should be simulated times.</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -974,7 +984,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Anchors of the net proliferation rates per cell type (get_proliferation_rates); every cell type needs a value.</t>
+          <t>Anchors of the proliferation rates per cell type (fit_population_anchors, get_proliferation_rates); every cell type needs a net rate, given directly or as birth - death. Birth and death, when given, anchor the two rates separately; otherwise the change of the net rate is shared between them. Rows with a sample_id anchor that sample only (a sample with rows of its own ignores the default ones); a sample without anchors borrows those of the best-fitting sample.</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -991,7 +1001,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Absolute population sizes, anchoring the growth estimated by optimal transport.</t>
+          <t>Population sizes per sample and time: they constrain the absolute growth in fit_population_anchors and in the growth estimated by optimal transport.</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1008,7 +1018,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Cell-type transition rate matrix constraining optimal transport: first column = source cell types, header = target cell types (as in obs cell_type_transition, else cell_type).</t>
+          <t>Cell-type transition rate matrix (Markov generator) constraining optimal transport through the probabilities expm(Q dt): first column = source cell types, header = target cell types (as in obs cell_type_transition, else cell_type). To give a matrix per sample, add a column sample_id right of the matrix (one value per row of the block, or one block per sample); rows without sample_id are the default of the samples without block of their own.</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1034,12 +1044,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="9" min="1" max="1"/>
     <col width="21" customWidth="1" style="9" min="2" max="2"/>
     <col width="16" customWidth="1" style="9" min="3" max="3"/>
+    <col width="23" customWidth="1" style="9" min="4" max="4"/>
+    <col width="23" customWidth="1" style="9" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1056,6 +1068,16 @@
       <c r="C1" s="10" t="inlineStr">
         <is>
           <t>sample_id</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>birth_rate_per_hour</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>death_rate_per_hour</t>
         </is>
       </c>
     </row>

--- a/experimental_datasets/Schiebinger/Data/CardamomOT_inputs.xlsx
+++ b/experimental_datasets/Schiebinger/Data/CardamomOT_inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eventre/Documents/GitHub/CardamomOT/experimental_datasets/Schiebinger/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2147E859-B9DE-4E41-B2DF-9359FE560B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19970B2-B138-9540-9A3E-01233E6C0F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -673,7 +673,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="220">
   <si>
     <t>genes_queries</t>
   </si>
@@ -735,9 +735,6 @@
     <t>Zfp42</t>
   </si>
   <si>
-    <t>Zpf42</t>
-  </si>
-  <si>
     <t>Dppa4</t>
   </si>
   <si>
@@ -871,75 +868,6 @@
   </si>
   <si>
     <t>Cyb5r3</t>
-  </si>
-  <si>
-    <t>Cenpm</t>
-  </si>
-  <si>
-    <t>Srebf2</t>
-  </si>
-  <si>
-    <t>Pmm1</t>
-  </si>
-  <si>
-    <t>Cdkn2a</t>
-  </si>
-  <si>
-    <t>Cdkn2b</t>
-  </si>
-  <si>
-    <t>Cdkn2c</t>
-  </si>
-  <si>
-    <t>Cdk13</t>
-  </si>
-  <si>
-    <t>Mapk9</t>
-  </si>
-  <si>
-    <t>Rarb</t>
-  </si>
-  <si>
-    <t>Foxp2</t>
-  </si>
-  <si>
-    <t>Emx1</t>
-  </si>
-  <si>
-    <t>Pou3f2</t>
-  </si>
-  <si>
-    <t>Nr2f1</t>
-  </si>
-  <si>
-    <t>Neurod4</t>
-  </si>
-  <si>
-    <t>Scrt2</t>
-  </si>
-  <si>
-    <t>Nhlh2</t>
-  </si>
-  <si>
-    <t>Pou2f2</t>
-  </si>
-  <si>
-    <t>Onecut1</t>
-  </si>
-  <si>
-    <t>Tal2</t>
-  </si>
-  <si>
-    <t>Barhl1</t>
-  </si>
-  <si>
-    <t>Pitx2</t>
-  </si>
-  <si>
-    <t>Msx1</t>
-  </si>
-  <si>
-    <t>Msx3</t>
   </si>
   <si>
     <t>CardamomOT — optional inputs of the run</t>
@@ -1827,26 +1755,26 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
     </row>
     <row r="3" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -1858,130 +1786,130 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -2008,19 +1936,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2041,13 +1969,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -2066,7 +1994,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -2087,432 +2015,432 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="B5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B10">
         <v>0.1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
     </row>
     <row r="36" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
     </row>
     <row r="42" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
     </row>
     <row r="49" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
     </row>
     <row r="53" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2523,7 +2451,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -2849,126 +2777,6 @@
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2987,16 +2795,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -3422,13 +3230,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -3447,16 +3255,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -3478,28 +3286,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -3518,15 +3326,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -3551,10 +3359,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/experimental_datasets/Schiebinger/Data/CardamomOT_inputs.xlsx
+++ b/experimental_datasets/Schiebinger/Data/CardamomOT_inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eventre/Documents/GitHub/CardamomOT/experimental_datasets/Schiebinger/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19970B2-B138-9540-9A3E-01233E6C0F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DFF8BD-3098-814C-83BB-82B3067EB436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -588,6 +588,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Timepoints of the test cells (split = train; 0 added if absent): times beyond the inference ones are held out for the test only; empty = the inference timepoints</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -673,7 +687,415 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="221">
+  <si>
+    <t>parameter</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Pipeline: steps and data</t>
+  </si>
+  <si>
+    <t>estimate_proliferation_rates</t>
+  </si>
+  <si>
+    <t>get_proliferation_rates: obs['proliferation_net_rate'] from gene signatures, anchored to Data/proliferation_rates</t>
+  </si>
+  <si>
+    <t>simulate_with_proliferation</t>
+  </si>
+  <si>
+    <t>apply branching process in simulate_trajectories_unitary</t>
+  </si>
+  <si>
+    <t>select_genes</t>
+  </si>
+  <si>
+    <t>select_genes_and_split: gene selection (queries, entropy genes, global network, Steiner tree); False = all genes kept</t>
+  </si>
+  <si>
+    <t>build_prior_network</t>
+  </si>
+  <si>
+    <t>literature prior cardamomOT/ref_network.csv: built by the gene selection if select_genes, else by build_reference_network</t>
+  </si>
+  <si>
+    <t>simulate_perturbations</t>
+  </si>
+  <si>
+    <t>simulate_network_KOV + check_KOV_to_sim (Data/KO_OV_Stim_simulate)</t>
+  </si>
+  <si>
+    <t>run_test</t>
+  </si>
+  <si>
+    <t>infer_test + check_test_to_train on the held-out cells (needs split = 'train')</t>
+  </si>
+  <si>
+    <t>split</t>
+  </si>
+  <si>
+    <t>'train': train/test split of the cells (train_rate per sample and time); 'full': all cells</t>
+  </si>
+  <si>
+    <t>train_rate</t>
+  </si>
+  <si>
+    <t>share of the cells of each (sample, time) in the train split (at least 100); the test keeps at most as many</t>
+  </si>
+  <si>
+    <t>species</t>
+  </si>
+  <si>
+    <t>'auto' (from gene names), 'human' or 'mouse': degradation rates, proliferation signatures, literature prior</t>
+  </si>
+  <si>
+    <t>Gene selection</t>
+  </si>
+  <si>
+    <t>num_max_genes</t>
+  </si>
+  <si>
+    <t>budget: number of selected genes (stimuli excluded)</t>
+  </si>
+  <si>
+    <t>n_query_genes</t>
+  </si>
+  <si>
+    <t>at most this many genes of Data/genes_queries.txt (round robin over time/cell-type DE groups)</t>
+  </si>
+  <si>
+    <t>n_entropy_genes</t>
+  </si>
+  <si>
+    <t>at least this many entropy genes (Gandrillon KD &amp; MDE), same round robin; n_query + n_entropy &lt; num_max_genes</t>
+  </si>
+  <si>
+    <t>network_method</t>
+  </si>
+  <si>
+    <t>global network: 'otvelo_granger', 'otvelo_corr', or &lt;project&gt;/network_methods/&lt;name&gt;.py</t>
+  </si>
+  <si>
+    <t>k_in_steiner</t>
+  </si>
+  <si>
+    <t>strongest incoming edges kept per gene in the Steiner graph</t>
+  </si>
+  <si>
+    <t>closure_min</t>
+  </si>
+  <si>
+    <t>closure: add the gene bringing the most probable regulation (sum of w) to the selection while &gt;= this</t>
+  </si>
+  <si>
+    <t>min_entropy_change</t>
+  </si>
+  <si>
+    <t>variability floor of the selection: max BUB-entropy change between consecutive times (bits, Gandrillon MDE)</t>
+  </si>
+  <si>
+    <t>min_nb_separation</t>
+  </si>
+  <si>
+    <t>... and separation of the extreme NB modes at the mixture initialization (times / cell types, batch_size_mixture cells per time)</t>
+  </si>
+  <si>
+    <t>Literature prior network</t>
+  </si>
+  <si>
+    <t>prior_network_pen</t>
+  </si>
+  <si>
+    <t>1 if we don't use prior information. If not we can penalize the non-existing age in prior network with values between 1 and 0: 0 = impossible edge</t>
+  </si>
+  <si>
+    <t>max_free_params</t>
+  </si>
+  <si>
+    <t>change=1 with ref=1 and prior 0 (hard prior): gene budget set so that the literature prior leaves this many free network parameters</t>
+  </si>
+  <si>
+    <t>literature_selection</t>
+  </si>
+  <si>
+    <t>reweight edge probabilities by OmniPath feasibility and write the literature prior (ref_network.csv)</t>
+  </si>
+  <si>
+    <t>literature_depth</t>
+  </si>
+  <si>
+    <t>max path length in the literature graph (last edge TF -&gt; target)</t>
+  </si>
+  <si>
+    <t>literature_resources</t>
+  </si>
+  <si>
+    <t>'extended' (OmniPath, CollecTRI + PathwayExtra, KinaseExtra, LigRecExtra, DoRothEA A-D, TFtarget) or 'core' (OmniPath + CollecTRI)</t>
+  </si>
+  <si>
+    <t>Stimulus</t>
+  </si>
+  <si>
+    <t>stimulus</t>
+  </si>
+  <si>
+    <t>1 if we simulate with a stimulus. If not we can penalize the stimulus with a value between 1 and 0: 0 = no sitmulus</t>
+  </si>
+  <si>
+    <t>Per-cell sequencing depth</t>
+  </si>
+  <si>
+    <t>use_depth_factor</t>
+  </si>
+  <si>
+    <t>use obs['depth_factor'] (estimate_cell_depth) in the NB model and simulations; False = s_i = 1 (an existing factor is kept but ignored)</t>
+  </si>
+  <si>
+    <t>compute_depth_factor</t>
+  </si>
+  <si>
+    <t>estimate_cell_depth computes the diagnostic and writes obs['depth_factor'] if needed; False = only reads an existing factor (never removed)</t>
+  </si>
+  <si>
+    <t>allow_depth_correction</t>
+  </si>
+  <si>
+    <t>estimate_cell_depth: apply the per-cell depth factor s_i when the diagnostic recommends it</t>
+  </si>
+  <si>
+    <t>depth_method</t>
+  </si>
+  <si>
+    <t>depth factor: 'group_median', 'poissonian' (Fang &amp; Pachter, 2025), or &lt;project&gt;/depth_methods/&lt;name&gt;.py</t>
+  </si>
+  <si>
+    <t>depth_by_cell_type</t>
+  </si>
+  <si>
+    <t>estimate s_i within (sample, time, cell type) groups; False = (sample, time) only:</t>
+  </si>
+  <si>
+    <t>NB mixture and samples</t>
+  </si>
+  <si>
+    <t>mean_forcing_em</t>
+  </si>
+  <si>
+    <t>at which point we force the mean correction: the higher the more</t>
+  </si>
+  <si>
+    <t>batch_size_mixture</t>
+  </si>
+  <si>
+    <t>Maximum number of cells per time used for mixture calibration in the inference.</t>
+  </si>
+  <si>
+    <t>soft_em_refinement</t>
+  </si>
+  <si>
+    <t>NB mixture: refine (ks, c) by soft EM with fixed basin masses</t>
+  </si>
+  <si>
+    <t>integrate_samples</t>
+  </si>
+  <si>
+    <t>in [0, 1]: per-sample mixtures pushed towards the common target (1 = equal parameters, 0 = own fits)</t>
+  </si>
+  <si>
+    <t>ref_sample_integration</t>
+  </si>
+  <si>
+    <t>dataset_id of the reference sample; None = cell-weighted average of mode means (keeps total counts)</t>
+  </si>
+  <si>
+    <t>Network inference</t>
+  </si>
+  <si>
+    <t>force_basins</t>
+  </si>
+  <si>
+    <t>Do we want to ensure the means to be preserved by the NB mixture ? It may not preserve multistability</t>
+  </si>
+  <si>
+    <t>temporal_basins</t>
+  </si>
+  <si>
+    <t>Is it preserved temporally ?</t>
+  </si>
+  <si>
+    <t>min_n_loops</t>
+  </si>
+  <si>
+    <t>minimal number of iterations in inference loops</t>
+  </si>
+  <si>
+    <t>max_iter</t>
+  </si>
+  <si>
+    <t>max iteration for main loop</t>
+  </si>
+  <si>
+    <t>batch_size_traj</t>
+  </si>
+  <si>
+    <t>Maximum number of cells used per time point per sample for solving EOT problems in the inference.</t>
+  </si>
+  <si>
+    <t>n_network_fits</t>
+  </si>
+  <si>
+    <t>Theta = mean of min(n_network_fits, 1 + n_states // batch_size) fits on disjoint subsamples, at every network update</t>
+  </si>
+  <si>
+    <t>Proliferation and simulation</t>
+  </si>
+  <si>
+    <t>growth_reg_source</t>
+  </si>
+  <si>
+    <t>source-marginal relaxation (x log G) of the growth OT pass: small = data-driven but noisy, large = prior kept</t>
+  </si>
+  <si>
+    <t>prolif_uses_stimulus</t>
+  </si>
+  <si>
+    <t>inference stimuli are inputs of the ProliferationMLP, R(u, P) (no effect if constant over the intervals)</t>
+  </si>
+  <si>
+    <t>simulation_stochastic</t>
+  </si>
+  <si>
+    <t>1 if we simulate Bursty-like proteins, 0 if deterministic limit for proteins</t>
+  </si>
+  <si>
+    <t>Reproducibility</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>Random seed for reproducibility (main process and parallel workers); None = not seeded (runs vary)</t>
+  </si>
+  <si>
+    <t>CardamomOT — optional inputs of the run</t>
+  </si>
+  <si>
+    <t>Fill only what you need: empty cells mean "not given" and the defaults of CardamomOT apply. Each sheet holds one kind of information; the header cells carry a comment (hover them) explaining their content.</t>
+  </si>
+  <si>
+    <t>Text files of older projects (genes_queries.txt, KO_OV_simulate.txt, stimulus_schedule.txt...) still present in Data/ are imported into this workbook at each run and OVERWRITE the corresponding cells (a warning is printed): delete them to edit the workbook instead.</t>
+  </si>
+  <si>
+    <t>Large numeric arrays stay files in Data/: reference_network.csv (structural prior), basal_init / basal_ref, inter_init / inter_ref (.npy or .csv), inter_simul_ref (.npy or .csv).</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>Replaces (older text files)</t>
+  </si>
+  <si>
+    <t>model_parameters</t>
+  </si>
+  <si>
+    <t>Parameters of the model for this project, grouped by use: empty value = default of CardamomOT/model/base.py; a filled value overrides it, and the command-line options override the workbook.</t>
+  </si>
+  <si>
+    <t>gene_lists</t>
+  </si>
+  <si>
+    <t>Gene lists, one gene per row in each column. Any other column is a named gene list, usable as the targets (STIMk) or a RATE target of perturbation_inference and perturbation_simulation (exported as gene_list_&lt;name&gt;.txt).</t>
+  </si>
+  <si>
+    <t>genes_queries.txt, proliferation_signatures.txt/.csv, death_signatures.txt/.csv, senescence_signatures.txt/.csv</t>
+  </si>
+  <si>
+    <t>stimulus_inference_schedule</t>
+  </si>
+  <si>
+    <t>Schedule of the stimuli of the measured data (inference); one row per timepoint, one column per stimulus (add stimulus_2, stimulus_3... for several stimuli; without this sheet: one stimulus). Rows with a sample_id give the schedule of that sample only (e.g. an untreated control at 0).</t>
+  </si>
+  <si>
+    <t>stimulus_schedule_inference.txt, stimulus_schedule.txt</t>
+  </si>
+  <si>
+    <t>stimulus_test_schedule</t>
+  </si>
+  <si>
+    <t>Schedule of the inference stimuli for the held-out cells (infer_test): test split and samples removed from the inference (perturbation_inference, remove_from_inference). Empty: the inference schedule.</t>
+  </si>
+  <si>
+    <t>stimulus_simulation_schedule</t>
+  </si>
+  <si>
+    <t>Schedules of the simulations: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation). Rows with a scenario name give alternative schedules (e.g. alternating inference and perturbation stimuli), simulated for the conditions that ask for them; a value applies to the simulated intervals ending at or after its time, so switching times should be simulated times.</t>
+  </si>
+  <si>
+    <t>stimulus_schedule_simulate.txt, stimulus_schedule_simul.txt</t>
+  </si>
+  <si>
+    <t>perturbation_inference</t>
+  </si>
+  <si>
+    <t>Perturbations of the measured data, used by the inference: genetic perturbations of samples (KO / OV), samples held out for validation (remove_from_inference, reference_sample), and the inference stimuli (row sample_id = all: targets STIMk and effects on proliferation RATEk, k = column of stimulus_inference_schedule). Empty: one stimulus, every gene a possible target, no effect on the rates.</t>
+  </si>
+  <si>
+    <t>KO_OV_inference.txt, stimulus_targets.txt/.csv</t>
+  </si>
+  <si>
+    <t>perturbation_simulation</t>
+  </si>
+  <si>
+    <t>In-silico perturbations simulated by simulate_network_KOV, one condition per row (add STIM2, STIM3... for several perturbation stimuli; their effects add up).</t>
+  </si>
+  <si>
+    <t>KO_OV_Stim_simulate.txt, KO_OV_simulate.txt</t>
+  </si>
+  <si>
+    <t>times</t>
+  </si>
+  <si>
+    <t>Timepoints, one per row.</t>
+  </si>
+  <si>
+    <t>times_to_inference.txt, times_to_simulate.txt</t>
+  </si>
+  <si>
+    <t>proliferation_rates</t>
+  </si>
+  <si>
+    <t>Anchors of the proliferation rates per cell type (fit_population_anchors, get_proliferation_rates); every cell type needs a net rate, given directly or as birth - death. Birth and death, when given, anchor the two rates separately; otherwise the change of the net rate is shared between them. Rows with a sample_id anchor that sample only (a sample with rows of its own ignores the default ones); a sample without anchors borrows those of the best-fitting sample.</t>
+  </si>
+  <si>
+    <t>proliferation_rates.txt/.csv</t>
+  </si>
+  <si>
+    <t>population_sizes</t>
+  </si>
+  <si>
+    <t>Population sizes per sample and time: they constrain the absolute growth in fit_population_anchors and in the growth estimated by optimal transport.</t>
+  </si>
+  <si>
+    <t>population_sizes.txt/.csv</t>
+  </si>
+  <si>
+    <t>transition_rates</t>
+  </si>
+  <si>
+    <t>Cell-type transition rate matrix (Markov generator) constraining optimal transport through the probabilities expm(Q dt): first column = source cell types, header = target cell types (as in obs cell_type_transition, else cell_type). To give a matrix per sample, add a column sample_id right of the matrix (one value per row of the block, or one block per sample); rows without sample_id are the default of the samples without block of their own.</t>
+  </si>
+  <si>
+    <t>transition_rates.txt/.csv</t>
+  </si>
   <si>
     <t>genes_queries</t>
   </si>
@@ -870,414 +1292,6 @@
     <t>Cyb5r3</t>
   </si>
   <si>
-    <t>CardamomOT — optional inputs of the run</t>
-  </si>
-  <si>
-    <t>Fill only what you need: empty cells mean "not given" and the defaults of CardamomOT apply. Each sheet holds one kind of information; the header cells carry a comment (hover them) explaining their content.</t>
-  </si>
-  <si>
-    <t>Text files of older projects (genes_queries.txt, KO_OV_simulate.txt, stimulus_schedule.txt...) still present in Data/ are imported into this workbook at each run and OVERWRITE the corresponding cells (a warning is printed): delete them to edit the workbook instead.</t>
-  </si>
-  <si>
-    <t>Large numeric arrays stay files in Data/: reference_network.csv (structural prior), basal_init / basal_ref, inter_init / inter_ref (.npy or .csv), inter_simul_ref (.npy or .csv).</t>
-  </si>
-  <si>
-    <t>Sheet</t>
-  </si>
-  <si>
-    <t>Content</t>
-  </si>
-  <si>
-    <t>Replaces (older text files)</t>
-  </si>
-  <si>
-    <t>model_parameters</t>
-  </si>
-  <si>
-    <t>Parameters of the model for this project, grouped by use: empty value = default of CardamomOT/model/base.py; a filled value overrides it, and the command-line options override the workbook.</t>
-  </si>
-  <si>
-    <t>gene_lists</t>
-  </si>
-  <si>
-    <t>Gene lists, one gene per row in each column. Any other column is a named gene list, usable as the targets (STIMk) or a RATE target of perturbation_inference and perturbation_simulation (exported as gene_list_&lt;name&gt;.txt).</t>
-  </si>
-  <si>
-    <t>genes_queries.txt, proliferation_signatures.txt/.csv, death_signatures.txt/.csv, senescence_signatures.txt/.csv</t>
-  </si>
-  <si>
-    <t>stimulus_inference_schedule</t>
-  </si>
-  <si>
-    <t>Schedule of the stimuli of the measured data (inference); one row per timepoint, one column per stimulus (add stimulus_2, stimulus_3... for several stimuli; without this sheet: one stimulus). Rows with a sample_id give the schedule of that sample only (e.g. an untreated control at 0).</t>
-  </si>
-  <si>
-    <t>stimulus_schedule_inference.txt, stimulus_schedule.txt</t>
-  </si>
-  <si>
-    <t>stimulus_test_schedule</t>
-  </si>
-  <si>
-    <t>Schedule of the inference stimuli for the held-out cells (infer_test): test split and samples removed from the inference (perturbation_inference, remove_from_inference). Empty: the inference schedule.</t>
-  </si>
-  <si>
-    <t>stimulus_simulation_schedule</t>
-  </si>
-  <si>
-    <t>Schedules of the simulations: inference stimuli (stimulus_k, acting on the genes and, through the RATEk of perturbation_inference, on proliferation and death), then perturbation stimuli (STIMk, as in perturbation_simulation). Rows with a scenario name give alternative schedules (e.g. alternating inference and perturbation stimuli), simulated for the conditions that ask for them; a value applies to the simulated intervals ending at or after its time, so switching times should be simulated times.</t>
-  </si>
-  <si>
-    <t>stimulus_schedule_simulate.txt, stimulus_schedule_simul.txt</t>
-  </si>
-  <si>
-    <t>perturbation_inference</t>
-  </si>
-  <si>
-    <t>Perturbations of the measured data, used by the inference: genetic perturbations of samples (KO / OV), samples held out for validation (remove_from_inference, reference_sample), and the inference stimuli (row sample_id = all: targets STIMk and effects on proliferation RATEk, k = column of stimulus_inference_schedule). Empty: one stimulus, every gene a possible target, no effect on the rates.</t>
-  </si>
-  <si>
-    <t>KO_OV_inference.txt, stimulus_targets.txt/.csv</t>
-  </si>
-  <si>
-    <t>perturbation_simulation</t>
-  </si>
-  <si>
-    <t>In-silico perturbations simulated by simulate_network_KOV, one condition per row (add STIM2, STIM3... for several perturbation stimuli; their effects add up).</t>
-  </si>
-  <si>
-    <t>KO_OV_Stim_simulate.txt, KO_OV_simulate.txt</t>
-  </si>
-  <si>
-    <t>times</t>
-  </si>
-  <si>
-    <t>Timepoints, one per row.</t>
-  </si>
-  <si>
-    <t>times_to_inference.txt, times_to_simulate.txt</t>
-  </si>
-  <si>
-    <t>proliferation_rates</t>
-  </si>
-  <si>
-    <t>Anchors of the proliferation rates per cell type (fit_population_anchors, get_proliferation_rates); every cell type needs a net rate, given directly or as birth - death. Birth and death, when given, anchor the two rates separately; otherwise the change of the net rate is shared between them. Rows with a sample_id anchor that sample only (a sample with rows of its own ignores the default ones); a sample without anchors borrows those of the best-fitting sample.</t>
-  </si>
-  <si>
-    <t>proliferation_rates.txt/.csv</t>
-  </si>
-  <si>
-    <t>population_sizes</t>
-  </si>
-  <si>
-    <t>Population sizes per sample and time: they constrain the absolute growth in fit_population_anchors and in the growth estimated by optimal transport.</t>
-  </si>
-  <si>
-    <t>population_sizes.txt/.csv</t>
-  </si>
-  <si>
-    <t>transition_rates</t>
-  </si>
-  <si>
-    <t>Cell-type transition rate matrix (Markov generator) constraining optimal transport through the probabilities expm(Q dt): first column = source cell types, header = target cell types (as in obs cell_type_transition, else cell_type). To give a matrix per sample, add a column sample_id right of the matrix (one value per row of the block, or one block per sample); rows without sample_id are the default of the samples without block of their own.</t>
-  </si>
-  <si>
-    <t>transition_rates.txt/.csv</t>
-  </si>
-  <si>
-    <t>parameter</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Pipeline: steps and data</t>
-  </si>
-  <si>
-    <t>estimate_proliferation_rates</t>
-  </si>
-  <si>
-    <t>get_proliferation_rates: obs['proliferation_net_rate'] from gene signatures, anchored to Data/proliferation_rates</t>
-  </si>
-  <si>
-    <t>simulate_with_proliferation</t>
-  </si>
-  <si>
-    <t>apply branching process in simulate_trajectories_unitary</t>
-  </si>
-  <si>
-    <t>select_genes</t>
-  </si>
-  <si>
-    <t>select_genes_and_split: gene selection (queries, entropy genes, global network, Steiner tree); False = all genes kept</t>
-  </si>
-  <si>
-    <t>build_prior_network</t>
-  </si>
-  <si>
-    <t>literature prior cardamomOT/ref_network.csv: built by the gene selection if select_genes, else by build_reference_network</t>
-  </si>
-  <si>
-    <t>simulate_perturbations</t>
-  </si>
-  <si>
-    <t>simulate_network_KOV + check_KOV_to_sim (Data/KO_OV_Stim_simulate)</t>
-  </si>
-  <si>
-    <t>run_test</t>
-  </si>
-  <si>
-    <t>infer_test + check_test_to_train on the held-out cells (needs split = 'train')</t>
-  </si>
-  <si>
-    <t>split</t>
-  </si>
-  <si>
-    <t>'train': train/test split of the cells (train_rate per sample and time); 'full': all cells</t>
-  </si>
-  <si>
-    <t>train_rate</t>
-  </si>
-  <si>
-    <t>share of the cells of each (sample, time) in the train split (at least 100); the test keeps at most as many</t>
-  </si>
-  <si>
-    <t>species</t>
-  </si>
-  <si>
-    <t>'auto' (from gene names), 'human' or 'mouse': degradation rates, proliferation signatures, literature prior</t>
-  </si>
-  <si>
-    <t>Gene selection</t>
-  </si>
-  <si>
-    <t>num_max_genes</t>
-  </si>
-  <si>
-    <t>budget: number of selected genes (stimuli excluded)</t>
-  </si>
-  <si>
-    <t>n_query_genes</t>
-  </si>
-  <si>
-    <t>at most this many genes of Data/genes_queries.txt (round robin over time/cell-type DE groups)</t>
-  </si>
-  <si>
-    <t>n_entropy_genes</t>
-  </si>
-  <si>
-    <t>at least this many entropy genes (Gandrillon KD &amp; MDE), same round robin; n_query + n_entropy &lt; num_max_genes</t>
-  </si>
-  <si>
-    <t>network_method</t>
-  </si>
-  <si>
-    <t>global network: 'otvelo_granger', 'otvelo_corr', or &lt;project&gt;/network_methods/&lt;name&gt;.py</t>
-  </si>
-  <si>
-    <t>k_in_steiner</t>
-  </si>
-  <si>
-    <t>strongest incoming edges kept per gene in the Steiner graph</t>
-  </si>
-  <si>
-    <t>closure_min</t>
-  </si>
-  <si>
-    <t>closure: add the gene bringing the most probable regulation (sum of w) to the selection while &gt;= this</t>
-  </si>
-  <si>
-    <t>min_entropy_change</t>
-  </si>
-  <si>
-    <t>variability floor of the selection: max BUB-entropy change between consecutive times (bits, Gandrillon MDE)</t>
-  </si>
-  <si>
-    <t>min_nb_separation</t>
-  </si>
-  <si>
-    <t>... and separation of the extreme NB modes at the mixture initialization (times / cell types, batch_size_mixture cells per time)</t>
-  </si>
-  <si>
-    <t>Literature prior network</t>
-  </si>
-  <si>
-    <t>prior_network_pen</t>
-  </si>
-  <si>
-    <t>1 if we don't use prior information. If not we can penalize the non-existing age in prior network with values between 1 and 0: 0 = impossible edge</t>
-  </si>
-  <si>
-    <t>max_free_params</t>
-  </si>
-  <si>
-    <t>change=1 with ref=1 and prior 0 (hard prior): gene budget set so that the literature prior leaves this many free network parameters</t>
-  </si>
-  <si>
-    <t>literature_selection</t>
-  </si>
-  <si>
-    <t>reweight edge probabilities by OmniPath feasibility and write the literature prior (ref_network.csv)</t>
-  </si>
-  <si>
-    <t>literature_depth</t>
-  </si>
-  <si>
-    <t>max path length in the literature graph (last edge TF -&gt; target)</t>
-  </si>
-  <si>
-    <t>literature_resources</t>
-  </si>
-  <si>
-    <t>'extended' (OmniPath, CollecTRI + PathwayExtra, KinaseExtra, LigRecExtra, DoRothEA A-D, TFtarget) or 'core' (OmniPath + CollecTRI)</t>
-  </si>
-  <si>
-    <t>Stimulus</t>
-  </si>
-  <si>
-    <t>stimulus</t>
-  </si>
-  <si>
-    <t>1 if we simulate with a stimulus. If not we can penalize the stimulus with a value between 1 and 0: 0 = no sitmulus</t>
-  </si>
-  <si>
-    <t>Per-cell sequencing depth</t>
-  </si>
-  <si>
-    <t>use_depth_factor</t>
-  </si>
-  <si>
-    <t>use obs['depth_factor'] (estimate_cell_depth) in the NB model and simulations; False = s_i = 1 (an existing factor is kept but ignored)</t>
-  </si>
-  <si>
-    <t>compute_depth_factor</t>
-  </si>
-  <si>
-    <t>estimate_cell_depth computes the diagnostic and writes obs['depth_factor'] if needed; False = only reads an existing factor (never removed)</t>
-  </si>
-  <si>
-    <t>allow_depth_correction</t>
-  </si>
-  <si>
-    <t>estimate_cell_depth: apply the per-cell depth factor s_i when the diagnostic recommends it</t>
-  </si>
-  <si>
-    <t>depth_method</t>
-  </si>
-  <si>
-    <t>depth factor: 'group_median', 'poissonian' (Fang &amp; Pachter, 2025), or &lt;project&gt;/depth_methods/&lt;name&gt;.py</t>
-  </si>
-  <si>
-    <t>depth_by_cell_type</t>
-  </si>
-  <si>
-    <t>estimate s_i within (sample, time, cell type) groups; False = (sample, time) only:</t>
-  </si>
-  <si>
-    <t>NB mixture and samples</t>
-  </si>
-  <si>
-    <t>mean_forcing_em</t>
-  </si>
-  <si>
-    <t>at which point we force the mean correction: the higher the more</t>
-  </si>
-  <si>
-    <t>batch_size_mixture</t>
-  </si>
-  <si>
-    <t>Maximum number of cells per time used for mixture calibration in the inference.</t>
-  </si>
-  <si>
-    <t>soft_em_refinement</t>
-  </si>
-  <si>
-    <t>NB mixture: refine (ks, c) by soft EM with fixed basin masses</t>
-  </si>
-  <si>
-    <t>integrate_samples</t>
-  </si>
-  <si>
-    <t>in [0, 1]: per-sample mixtures pushed towards the common target (1 = equal parameters, 0 = own fits)</t>
-  </si>
-  <si>
-    <t>ref_sample_integration</t>
-  </si>
-  <si>
-    <t>dataset_id of the reference sample; None = cell-weighted average of mode means (keeps total counts)</t>
-  </si>
-  <si>
-    <t>Network inference</t>
-  </si>
-  <si>
-    <t>force_basins</t>
-  </si>
-  <si>
-    <t>Do we want to ensure the means to be preserved by the NB mixture ? It may not preserve multistability</t>
-  </si>
-  <si>
-    <t>temporal_basins</t>
-  </si>
-  <si>
-    <t>Is it preserved temporally ?</t>
-  </si>
-  <si>
-    <t>min_n_loops</t>
-  </si>
-  <si>
-    <t>minimal number of iterations in inference loops</t>
-  </si>
-  <si>
-    <t>max_iter</t>
-  </si>
-  <si>
-    <t>max iteration for main loop</t>
-  </si>
-  <si>
-    <t>batch_size_traj</t>
-  </si>
-  <si>
-    <t>Maximum number of cells used per time point per sample for solving EOT problems in the inference.</t>
-  </si>
-  <si>
-    <t>n_network_fits</t>
-  </si>
-  <si>
-    <t>Theta = mean of min(n_network_fits, 1 + n_states // batch_size) fits on disjoint subsamples, at every network update</t>
-  </si>
-  <si>
-    <t>Proliferation and simulation</t>
-  </si>
-  <si>
-    <t>growth_reg_source</t>
-  </si>
-  <si>
-    <t>source-marginal relaxation (x log G) of the growth OT pass: small = data-driven but noisy, large = prior kept</t>
-  </si>
-  <si>
-    <t>prolif_uses_stimulus</t>
-  </si>
-  <si>
-    <t>inference stimuli are inputs of the ProliferationMLP, R(u, P) (no effect if constant over the intervals)</t>
-  </si>
-  <si>
-    <t>simulation_stochastic</t>
-  </si>
-  <si>
-    <t>1 if we simulate Bursty-like proteins, 0 if deterministic limit for proteins</t>
-  </si>
-  <si>
-    <t>Reproducibility</t>
-  </si>
-  <si>
-    <t>seed</t>
-  </si>
-  <si>
-    <t>Random seed for reproducibility (main process and parallel workers); None = not seeded (runs vary)</t>
-  </si>
-  <si>
     <t>sample_id</t>
   </si>
   <si>
@@ -1311,10 +1325,13 @@
     <t>comment</t>
   </si>
   <si>
-    <t>times_to_inference</t>
-  </si>
-  <si>
-    <t>times_to_simulate</t>
+    <t>times_inference</t>
+  </si>
+  <si>
+    <t>times_simulation</t>
+  </si>
+  <si>
+    <t>times_test</t>
   </si>
   <si>
     <t>cell_type</t>
@@ -1339,7 +1356,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1380,8 +1397,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1408,6 +1432,11 @@
         <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1421,7 +1450,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1437,6 +1466,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1755,161 +1787,161 @@
   <sheetData>
     <row r="1" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
+      <c r="A2" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
     </row>
     <row r="3" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10"/>
+      <c r="A3" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
+      <c r="A4" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>96</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>99</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1936,19 +1968,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>201</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -1972,7 +2004,7 @@
         <v>202</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>201</v>
@@ -1994,7 +2026,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -2015,432 +2047,432 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>105</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
     </row>
     <row r="3" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>108</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="B5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>116</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>0.1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>129</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>137</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>139</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>141</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>142</v>
+        <v>39</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>40</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>144</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>145</v>
+        <v>42</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>146</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>148</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>149</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>150</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>152</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>153</v>
+        <v>50</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>154</v>
+        <v>51</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>155</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>163</v>
+        <v>60</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>164</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>165</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>166</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>167</v>
+        <v>64</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
     </row>
     <row r="36" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>168</v>
+        <v>65</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>169</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>170</v>
+        <v>67</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>171</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>172</v>
+        <v>69</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>173</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>174</v>
+        <v>71</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>175</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>177</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>178</v>
+        <v>75</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
     </row>
     <row r="42" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>179</v>
+        <v>76</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>180</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>181</v>
+        <v>78</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>183</v>
+        <v>80</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>184</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>186</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>189</v>
+        <v>86</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>190</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>191</v>
+        <v>88</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
     </row>
     <row r="49" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>192</v>
+        <v>89</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>193</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>195</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>197</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>198</v>
+        <v>95</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
     </row>
     <row r="53" spans="1:3" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>199</v>
+        <v>96</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>200</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2462,321 +2494,321 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>2</v>
+        <v>138</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>172</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>48</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>49</v>
+        <v>185</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>50</v>
+        <v>186</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>52</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>56</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>195</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>199</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3334,12 +3366,12 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
-        <v>31</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
-        <v>19</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -3350,19 +3382,23 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>212</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>213</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
